--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -27,12 +27,6 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-method-collection</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet#urn:oid:2.16.840.1.113883.2.8.1.3.31</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
@@ -66,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -254,7 +248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -343,15 +337,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -369,28 +363,20 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -409,28 +395,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
